--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalven 225 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 450 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -819,7 +819,7 @@
         <v>136370093</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,61 +955,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136352733</v>
+        <v>136390346</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521191</v>
+        <v>521171</v>
       </c>
       <c r="R4" t="n">
-        <v>6637198</v>
+        <v>6637361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,7 +1041,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hackmärken i tallåga</t>
+          <t>minst 20 bålar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,6 +1050,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1065,22 +1061,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # på stam och grenar på torrträd med delvis kvarsittande bark # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1097,70 +1093,65 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352733</t>
+          <t>https://artportalen.se/Sighting/136390346</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136369839</v>
+        <v>136390391</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 275 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521218</v>
+        <v>521174</v>
       </c>
       <c r="R5" t="n">
-        <v>6637248</v>
+        <v>6637399</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1194,7 +1185,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hackmärken i talltorraka</t>
+          <t>Cirka 10 bålar på grenar på torrgran och 3 bålar på levande klen gran, på kvist.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1203,6 +1194,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1213,12 +1205,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1228,7 +1220,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # och på klent levande träd # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1245,38 +1237,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369839</t>
+          <t>https://artportalen.se/Sighting/136390391</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136370426</v>
+        <v>136390547</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1284,31 +1276,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 180 m V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521173</v>
+        <v>521206</v>
       </c>
       <c r="R6" t="n">
-        <v>6637338</v>
+        <v>6637452</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1340,17 +1327,13 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hackmärken i basen av grov granhögstubbe</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1369,14 +1352,22 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>klent träd</t>
+        </is>
+      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>1 substratenheter # Branch on living tree # död kvist # Picea abies # klent träd</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1393,38 +1384,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370426</t>
+          <t>https://artportalen.se/Sighting/136390547</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136352753</v>
+        <v>136390574</v>
       </c>
       <c r="B7" t="n">
-        <v>57175</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1432,28 +1423,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521128</v>
+        <v>521217</v>
       </c>
       <c r="R7" t="n">
-        <v>6637213</v>
+        <v>6637375</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1488,23 +1474,47 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>spillning på grov tallåga</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Branch on living tree # död kvist # Picea abies # grovt träd</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1521,59 +1531,62 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352753</t>
+          <t>https://artportalen.se/Sighting/136390574</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136370107</v>
+        <v>136390613</v>
       </c>
       <c r="B8" t="n">
-        <v>106330</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221154</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521195</v>
+        <v>521227</v>
       </c>
       <c r="R8" t="n">
-        <v>6637298</v>
+        <v>6637369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1608,6 +1621,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>minst tre stora bålar</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1623,6 +1641,26 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Dead branch  # död gren på grovt levande träd # Picea abies</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1637,54 +1675,62 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370107</t>
+          <t>https://artportalen.se/Sighting/136390613</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136369811</v>
+        <v>136390682</v>
       </c>
       <c r="B9" t="n">
-        <v>79054</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228595</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulvit renlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia arbuscula</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wallr.) Flot.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521218</v>
+        <v>521216</v>
       </c>
       <c r="R9" t="n">
-        <v>6637248</v>
+        <v>6637370</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1734,6 +1780,31 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Dead branch  # död kvist på grovt levande träd # Picea abies # grovt träd</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1748,38 +1819,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369811</t>
+          <t>https://artportalen.se/Sighting/136390682</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136369816</v>
+        <v>136391062</v>
       </c>
       <c r="B10" t="n">
-        <v>79131</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228654</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1788,14 +1859,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521218</v>
+        <v>521225</v>
       </c>
       <c r="R10" t="n">
-        <v>6637248</v>
+        <v>6637365</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1845,6 +1916,31 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>klent träd</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # torrgran # Picea abies # klent träd</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1859,54 +1955,62 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369816</t>
+          <t>https://artportalen.se/Sighting/136391062</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136369808</v>
+        <v>136391089</v>
       </c>
       <c r="B11" t="n">
-        <v>79138</v>
+        <v>79460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228659</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fönsterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia stellaris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Opiz) Pouzar &amp; Vezda</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521218</v>
+        <v>521228</v>
       </c>
       <c r="R11" t="n">
-        <v>6637248</v>
+        <v>6637353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1956,6 +2060,31 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1969,6 +2098,1873 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391089</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136391098</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>521238</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6637348</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391098</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136391109</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>521242</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6637354</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391109</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136391139</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>521237</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6637345</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>levande klent träd</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande klent träd</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391139</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136391147</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>521235</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6637338</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391147</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136391158</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>521239</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6637335</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391158</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136391189</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>521231</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6637340</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>en bål på klen torrkvist på en klen liten gran och en bål på död gren på grov levande gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391189</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136352733</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>521191</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6637198</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska hackmärken i tallåga</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136352733</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136369839</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>hackmärken i talltorraka</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369839</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136370426</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>521173</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6637338</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hackmärken i basen av grov granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136370426</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136352753</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57180</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>521128</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6637213</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>spillning på grov tallåga</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136352753</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136370107</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106343</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>521195</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6637298</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136370107</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136369811</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79060</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228595</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gulvit renlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cladonia arbuscula</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Wallr.) Flot.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369811</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136369816</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79137</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369816</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136369808</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79144</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136369808</t>
         </is>
@@ -1986,6 +3982,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,56 +816,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136370093</v>
+        <v>136418477</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521195</v>
+        <v>521208</v>
       </c>
       <c r="R3" t="n">
-        <v>6637298</v>
+        <v>6637184</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,6 +897,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -917,22 +919,25 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
-        </is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # och på stammen # Picea abies</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # grov låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,62 +954,59 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370093</t>
+          <t>https://artportalen.se/Sighting/136418477</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136390346</v>
+        <v>136418555</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521171</v>
+        <v>521202</v>
       </c>
       <c r="R4" t="n">
-        <v>6637361</v>
+        <v>6637212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,7 +1043,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>minst 20 bålar</t>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,22 +1063,25 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # på stam och grenar på torrträd med delvis kvarsittande bark # Picea abies</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # grov låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1093,13 +1098,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136390346</t>
+          <t>https://artportalen.se/Sighting/136418555</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136390391</v>
+        <v>136370093</v>
       </c>
       <c r="B5" t="n">
         <v>79460</v>
@@ -1129,7 +1134,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1141,14 +1146,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kalven 275 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521174</v>
+        <v>521195</v>
       </c>
       <c r="R5" t="n">
-        <v>6637399</v>
+        <v>6637298</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1183,11 +1188,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Cirka 10 bålar på grenar på torrgran och 3 bålar på levande klen gran, på kvist.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # och på klent levande träd # Picea abies</t>
+          <t>Branch on living tree # och på stammen # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1237,13 +1237,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136390391</t>
+          <t>https://artportalen.se/Sighting/136370093</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136390547</v>
+        <v>136390346</v>
       </c>
       <c r="B6" t="n">
         <v>79460</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1285,17 +1285,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kalven 180 m V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521206</v>
+        <v>521171</v>
       </c>
       <c r="R6" t="n">
-        <v>6637452</v>
+        <v>6637361</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1325,6 +1325,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>minst 20 bålar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1352,22 +1357,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>klent träd</t>
-        </is>
-      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # Branch on living tree # död kvist # Picea abies # klent träd</t>
+          <t>Standing dead tree/snags # på stam och grenar på torrträd med delvis kvarsittande bark # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1384,13 +1381,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136390547</t>
+          <t>https://artportalen.se/Sighting/136390346</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136390574</v>
+        <v>136390391</v>
       </c>
       <c r="B7" t="n">
         <v>79460</v>
@@ -1420,7 +1417,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1432,14 +1429,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 275 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521217</v>
+        <v>521174</v>
       </c>
       <c r="R7" t="n">
-        <v>6637375</v>
+        <v>6637399</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1474,6 +1471,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Cirka 10 bålar på grenar på torrgran och 3 bålar på levande klen gran, på kvist.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1499,22 +1501,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>grovt träd</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # Branch on living tree # död kvist # Picea abies # grovt träd</t>
+          <t>Standing dead tree/snags # och på klent levande träd # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1531,13 +1525,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136390574</t>
+          <t>https://artportalen.se/Sighting/136390391</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136390613</v>
+        <v>136390547</v>
       </c>
       <c r="B8" t="n">
         <v>79460</v>
@@ -1567,7 +1561,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1579,17 +1573,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 180 m V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521227</v>
+        <v>521206</v>
       </c>
       <c r="R8" t="n">
-        <v>6637369</v>
+        <v>6637452</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1619,11 +1613,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>minst tre stora bålar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1651,14 +1640,22 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>klent träd</t>
+        </is>
+      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Död gren</t>
-        </is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Dead branch  # död gren på grovt levande träd # Picea abies</t>
+          <t>1 substratenheter # Branch on living tree # död kvist # Picea abies # klent träd</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1675,13 +1672,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136390613</t>
+          <t>https://artportalen.se/Sighting/136390547</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136390682</v>
+        <v>136390574</v>
       </c>
       <c r="B9" t="n">
         <v>79460</v>
@@ -1727,10 +1724,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521216</v>
+        <v>521217</v>
       </c>
       <c r="R9" t="n">
-        <v>6637370</v>
+        <v>6637375</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1797,12 +1794,15 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Död gren</t>
-        </is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Dead branch  # död kvist på grovt levande träd # Picea abies # grovt träd</t>
+          <t>1 substratenheter # Branch on living tree # död kvist # Picea abies # grovt träd</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1819,13 +1819,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136390682</t>
+          <t>https://artportalen.se/Sighting/136390574</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136391062</v>
+        <v>136390613</v>
       </c>
       <c r="B10" t="n">
         <v>79460</v>
@@ -1853,20 +1853,28 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521225</v>
+        <v>521227</v>
       </c>
       <c r="R10" t="n">
-        <v>6637365</v>
+        <v>6637369</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1901,6 +1909,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>minst tre stora bålar</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1926,19 +1939,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>klent träd</t>
-        </is>
-      </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # torrgran # Picea abies # klent träd</t>
+          <t>Dead branch  # död gren på grovt levande träd # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1955,13 +1963,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391062</t>
+          <t>https://artportalen.se/Sighting/136390613</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136391089</v>
+        <v>136390682</v>
       </c>
       <c r="B11" t="n">
         <v>79460</v>
@@ -2003,14 +2011,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521228</v>
+        <v>521216</v>
       </c>
       <c r="R11" t="n">
-        <v>6637353</v>
+        <v>6637370</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2072,7 +2080,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>levande träd</t>
+          <t>grovt träd</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2082,7 +2090,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # levande träd</t>
+          <t>Dead branch  # död kvist på grovt levande träd # Picea abies # grovt träd</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2099,13 +2107,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391089</t>
+          <t>https://artportalen.se/Sighting/136390682</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136391098</v>
+        <v>136391062</v>
       </c>
       <c r="B12" t="n">
         <v>79460</v>
@@ -2133,16 +2141,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521238</v>
+        <v>521225</v>
       </c>
       <c r="R12" t="n">
-        <v>6637348</v>
+        <v>6637365</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2216,17 +2216,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>levande träd</t>
+          <t>klent träd</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # levande träd</t>
+          <t>Standing dead tree/snags # torrgran # Picea abies # klent träd</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2243,13 +2243,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391098</t>
+          <t>https://artportalen.se/Sighting/136391062</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136391109</v>
+        <v>136391089</v>
       </c>
       <c r="B13" t="n">
         <v>79460</v>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521242</v>
+        <v>521228</v>
       </c>
       <c r="R13" t="n">
-        <v>6637354</v>
+        <v>6637353</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2387,13 +2387,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391109</t>
+          <t>https://artportalen.se/Sighting/136391089</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136391139</v>
+        <v>136391098</v>
       </c>
       <c r="B14" t="n">
         <v>79460</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521237</v>
+        <v>521238</v>
       </c>
       <c r="R14" t="n">
-        <v>6637345</v>
+        <v>6637348</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>levande klent träd</t>
+          <t>levande träd</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # levande klent träd</t>
+          <t>Dead branch  # Picea abies # levande träd</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2531,13 +2531,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391139</t>
+          <t>https://artportalen.se/Sighting/136391098</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136391147</v>
+        <v>136391109</v>
       </c>
       <c r="B15" t="n">
         <v>79460</v>
@@ -2565,8 +2565,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2575,10 +2583,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521235</v>
+        <v>521242</v>
       </c>
       <c r="R15" t="n">
-        <v>6637338</v>
+        <v>6637354</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2638,6 +2646,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
       <c r="AM15" t="inlineStr">
         <is>
           <t>Död gren</t>
@@ -2645,7 +2658,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Dead branch  # Picea abies # levande träd</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2662,13 +2675,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391147</t>
+          <t>https://artportalen.se/Sighting/136391109</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136391158</v>
+        <v>136391139</v>
       </c>
       <c r="B16" t="n">
         <v>79460</v>
@@ -2698,7 +2711,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2714,10 +2727,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521239</v>
+        <v>521237</v>
       </c>
       <c r="R16" t="n">
-        <v>6637335</v>
+        <v>6637345</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2777,6 +2790,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>levande klent träd</t>
+        </is>
+      </c>
       <c r="AM16" t="inlineStr">
         <is>
           <t>Död gren</t>
@@ -2784,7 +2802,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Dead branch  # Picea abies # levande klent träd</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2801,13 +2819,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391158</t>
+          <t>https://artportalen.se/Sighting/136391139</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136391189</v>
+        <v>136391147</v>
       </c>
       <c r="B17" t="n">
         <v>79460</v>
@@ -2835,16 +2853,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2853,10 +2863,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521231</v>
+        <v>521235</v>
       </c>
       <c r="R17" t="n">
-        <v>6637340</v>
+        <v>6637338</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2891,11 +2901,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>en bål på klen torrkvist på en klen liten gran och en bål på död gren på grov levande gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2945,67 +2950,62 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391189</t>
+          <t>https://artportalen.se/Sighting/136391147</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136352733</v>
+        <v>136391158</v>
       </c>
       <c r="B18" t="n">
-        <v>57990</v>
+        <v>79460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521191</v>
+        <v>521239</v>
       </c>
       <c r="R18" t="n">
-        <v>6637198</v>
+        <v>6637335</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3040,17 +3040,13 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska hackmärken i tallåga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3061,22 +3057,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3093,70 +3089,65 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352733</t>
+          <t>https://artportalen.se/Sighting/136391158</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136369839</v>
+        <v>136391189</v>
       </c>
       <c r="B19" t="n">
-        <v>57990</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521218</v>
+        <v>521231</v>
       </c>
       <c r="R19" t="n">
-        <v>6637248</v>
+        <v>6637340</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3190,7 +3181,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>hackmärken i talltorraka</t>
+          <t>en bål på klen torrkvist på en klen liten gran och en bål på död gren på grov levande gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3199,6 +3190,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3209,22 +3201,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3241,38 +3233,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369839</t>
+          <t>https://artportalen.se/Sighting/136391189</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136370426</v>
+        <v>136418441</v>
       </c>
       <c r="B20" t="n">
-        <v>57990</v>
+        <v>79460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3280,28 +3272,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521173</v>
+        <v>521222</v>
       </c>
       <c r="R20" t="n">
-        <v>6637338</v>
+        <v>6637167</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3336,17 +3323,13 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hackmärken i basen av grov granhögstubbe</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3365,14 +3348,22 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>1 substratenheter # Branch on living tree # torrkvist # Picea abies # grovt träd</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3389,67 +3380,62 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370426</t>
+          <t>https://artportalen.se/Sighting/136418441</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136352753</v>
+        <v>136418448</v>
       </c>
       <c r="B21" t="n">
-        <v>57180</v>
+        <v>79460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521128</v>
+        <v>521217</v>
       </c>
       <c r="R21" t="n">
-        <v>6637213</v>
+        <v>6637164</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3484,23 +3470,47 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>spillning på grov tallåga</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Branch on living tree # torrkvistar # Picea abies # grovt träd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3517,59 +3527,62 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352753</t>
+          <t>https://artportalen.se/Sighting/136418448</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136370107</v>
+        <v>136418460</v>
       </c>
       <c r="B22" t="n">
-        <v>106343</v>
+        <v>79460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221154</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521195</v>
+        <v>521226</v>
       </c>
       <c r="R22" t="n">
-        <v>6637298</v>
+        <v>6637168</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3619,6 +3632,34 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Branch on living tree # torrkvist # Picea abies # grovt träd</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
@@ -3633,16 +3674,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370107</t>
+          <t>https://artportalen.se/Sighting/136418460</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136369811</v>
+        <v>136352733</v>
       </c>
       <c r="B23" t="n">
-        <v>79060</v>
+        <v>57990</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3650,37 +3691,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228595</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulvit renlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia arbuscula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wallr.) Flot.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521218</v>
+        <v>521191</v>
       </c>
       <c r="R23" t="n">
-        <v>6637248</v>
+        <v>6637198</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3715,19 +3769,43 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska hackmärken i tallåga</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3744,16 +3822,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369811</t>
+          <t>https://artportalen.se/Sighting/136352733</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136369816</v>
+        <v>136369839</v>
       </c>
       <c r="B24" t="n">
-        <v>79137</v>
+        <v>57990</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3761,27 +3839,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228654</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
@@ -3794,7 +3885,7 @@
         <v>6637248</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3826,19 +3917,43 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>hackmärken i talltorraka</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3855,16 +3970,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369816</t>
+          <t>https://artportalen.se/Sighting/136369839</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136369808</v>
+        <v>136370426</v>
       </c>
       <c r="B25" t="n">
-        <v>79144</v>
+        <v>57990</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3872,37 +3987,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228659</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fönsterlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia stellaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Opiz) Pouzar &amp; Vezda</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521218</v>
+        <v>521173</v>
       </c>
       <c r="R25" t="n">
-        <v>6637248</v>
+        <v>6637338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3937,19 +4065,43 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hackmärken i basen av grov granhögstubbe</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3965,6 +4117,583 @@
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136370426</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136352753</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57180</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>521128</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6637213</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>spillning på grov tallåga</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136352753</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136370107</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106343</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>521195</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6637298</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136370107</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136369811</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79060</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228595</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gulvit renlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cladonia arbuscula</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Wallr.) Flot.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369811</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136369816</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79137</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369816</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136369808</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79144</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136369808</t>
         </is>
@@ -3996,6 +4725,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136418477</v>
       </c>
       <c r="B3" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>136418555</v>
       </c>
       <c r="B4" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136370107</v>
       </c>
       <c r="B27" t="n">
-        <v>106343</v>
+        <v>106344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136418477</v>
       </c>
       <c r="B3" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>136418555</v>
       </c>
       <c r="B4" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136370093</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136390346</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>136390391</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136390547</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136390574</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136390613</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136390682</v>
       </c>
       <c r="B11" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136391062</v>
       </c>
       <c r="B12" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136391089</v>
       </c>
       <c r="B13" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136391098</v>
       </c>
       <c r="B14" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136391109</v>
       </c>
       <c r="B15" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>136391139</v>
       </c>
       <c r="B16" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>136391147</v>
       </c>
       <c r="B17" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>136391158</v>
       </c>
       <c r="B18" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136391189</v>
       </c>
       <c r="B19" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136418441</v>
       </c>
       <c r="B20" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136418448</v>
       </c>
       <c r="B21" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136418460</v>
       </c>
       <c r="B22" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136352733</v>
       </c>
       <c r="B23" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>136369839</v>
       </c>
       <c r="B24" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136370426</v>
       </c>
       <c r="B25" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>136352753</v>
       </c>
       <c r="B26" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136370107</v>
       </c>
       <c r="B27" t="n">
-        <v>106344</v>
+        <v>106357</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136369811</v>
       </c>
       <c r="B28" t="n">
-        <v>79060</v>
+        <v>79073</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>136369816</v>
       </c>
       <c r="B29" t="n">
-        <v>79137</v>
+        <v>79150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>136369808</v>
       </c>
       <c r="B30" t="n">
-        <v>79144</v>
+        <v>79157</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136418477</v>
       </c>
       <c r="B3" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>136418555</v>
       </c>
       <c r="B4" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136370093</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136390346</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>136390391</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136390547</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136390574</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136390613</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136390682</v>
       </c>
       <c r="B11" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136391062</v>
       </c>
       <c r="B12" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136391089</v>
       </c>
       <c r="B13" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136391098</v>
       </c>
       <c r="B14" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136391109</v>
       </c>
       <c r="B15" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>136391139</v>
       </c>
       <c r="B16" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>136391147</v>
       </c>
       <c r="B17" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>136391158</v>
       </c>
       <c r="B18" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136391189</v>
       </c>
       <c r="B19" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136418441</v>
       </c>
       <c r="B20" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136418448</v>
       </c>
       <c r="B21" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136418460</v>
       </c>
       <c r="B22" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136370107</v>
       </c>
       <c r="B27" t="n">
-        <v>106357</v>
+        <v>106358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136369811</v>
       </c>
       <c r="B28" t="n">
-        <v>79073</v>
+        <v>79074</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>136369816</v>
       </c>
       <c r="B29" t="n">
-        <v>79150</v>
+        <v>79151</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>136369808</v>
       </c>
       <c r="B30" t="n">
-        <v>79157</v>
+        <v>79158</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
